--- a/Payments.xlsx
+++ b/Payments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\USER-PC\Ravens\Senior Open 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E1A7F31-FF73-48A9-8928-1257EF67563A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E852B6-D62F-4248-85E8-BEBD3B75BFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{20FD19A6-D5EB-470E-BA3E-64F28732135B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="99">
   <si>
     <t>Le Roux Strydom</t>
   </si>
@@ -221,9 +221,6 @@
     <t xml:space="preserve">Boundary </t>
   </si>
   <si>
-    <t>Tamika Van Aa</t>
-  </si>
-  <si>
     <t>Boundary</t>
   </si>
   <si>
@@ -278,16 +275,10 @@
     <t>Rogan Fortuin</t>
   </si>
   <si>
-    <t>Ezra Msindeni</t>
-  </si>
-  <si>
     <t>Shane Overmayer</t>
   </si>
   <si>
     <t>Bounce TTC</t>
-  </si>
-  <si>
-    <t>Demos Dracoulides</t>
   </si>
   <si>
     <t>Denver Sweatz</t>
@@ -585,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -593,9 +584,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
@@ -721,24 +709,6 @@
           <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color auto="1"/>
@@ -754,6 +724,24 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -780,13 +768,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color auto="1"/>
         </left>
@@ -798,6 +779,13 @@
         </top>
         <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
         </bottom>
       </border>
     </dxf>
@@ -837,14 +825,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C3AAE3A1-2292-44A8-9A60-4F25F509993E}" name="Table1" displayName="Table1" ref="A1:C85" totalsRowCount="1" headerRowBorderDxfId="5" tableBorderDxfId="6">
-  <autoFilter ref="A1:C84" xr:uid="{C3AAE3A1-2292-44A8-9A60-4F25F509993E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C84">
-    <sortCondition ref="B1:B84"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C3AAE3A1-2292-44A8-9A60-4F25F509993E}" name="Table1" displayName="Table1" ref="A1:C82" totalsRowCount="1" headerRowBorderDxfId="6" tableBorderDxfId="5">
+  <autoFilter ref="A1:C81" xr:uid="{C3AAE3A1-2292-44A8-9A60-4F25F509993E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C81">
+    <sortCondition ref="B1:B81"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{7626E09E-2B1B-418C-9849-29381AA54924}" name="Name" dataDxfId="4" totalsRowDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{16A0F98D-43CC-4CB8-8BA0-7D19F26407D7}" name="Club" dataDxfId="3" totalsRowDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{7626E09E-2B1B-418C-9849-29381AA54924}" name="Name" dataDxfId="4" totalsRowDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{16A0F98D-43CC-4CB8-8BA0-7D19F26407D7}" name="Club" dataDxfId="2" totalsRowDxfId="1"/>
     <tableColumn id="3" xr3:uid="{3EE74F1F-3239-48C8-9A34-81F7D990581E}" name="Paid" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1168,96 +1156,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CA27C5-37ED-429D-8AC1-0ED926991F49}">
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>101</v>
+      <c r="A1" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="24" t="b">
+      <c r="C2" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="B5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="11" t="b">
+      <c r="C5" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>61</v>
+      <c r="A6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="C6" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="11" t="b">
+      <c r="A7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="A8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="10" t="b">
@@ -1265,21 +1253,21 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="11" t="b">
+      <c r="C9" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C10" s="10" t="b">
@@ -1287,43 +1275,43 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="11" t="b">
+      <c r="C11" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="A12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="A13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="11" t="b">
-        <v>0</v>
+      <c r="C13" s="9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="A14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="10" t="b">
@@ -1331,43 +1319,43 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="11" t="b">
+      <c r="C15" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>33</v>
+      <c r="A16" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="C16" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="11" t="b">
+      <c r="C17" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="1" t="s">
+      <c r="A18" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="10" t="b">
@@ -1375,21 +1363,21 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="A19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="11" t="b">
+      <c r="C19" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="A20" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C20" s="10" t="b">
@@ -1397,32 +1385,32 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="A21" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="11" t="b">
+      <c r="C21" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="10" t="b">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="C22" s="9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="A23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C23" s="10" t="b">
@@ -1430,21 +1418,21 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="A24" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="11" t="b">
+      <c r="C24" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="1" t="s">
+      <c r="A25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C25" s="10" t="b">
@@ -1452,21 +1440,21 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="2" t="s">
+      <c r="A26" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="11" t="b">
+      <c r="C26" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="A27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="10" t="b">
@@ -1474,43 +1462,43 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="A28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="11" t="b">
+      <c r="C28" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>5</v>
+      <c r="A29" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="C29" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="2" t="s">
+      <c r="A30" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="11" t="b">
+      <c r="C30" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B31" s="1" t="s">
+      <c r="A31" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C31" s="10" t="b">
@@ -1518,21 +1506,21 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="2" t="s">
+      <c r="A32" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="11" t="b">
+      <c r="C32" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" s="1" t="s">
+      <c r="A33" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="10" t="b">
@@ -1540,21 +1528,21 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B34" s="2" t="s">
+      <c r="A34" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="11" t="b">
+      <c r="C34" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B35" s="1" t="s">
+      <c r="A35" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="10" t="b">
@@ -1562,54 +1550,54 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B36" s="2" t="s">
+      <c r="A36" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="11" t="b">
+      <c r="C36" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="10" t="b">
-        <v>1</v>
+        <v>63</v>
+      </c>
+      <c r="C37" s="9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>64</v>
+      <c r="A38" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="C38" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="11" t="b">
+      <c r="A39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B40" s="1" t="s">
+      <c r="A40" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C40" s="10" t="b">
@@ -1617,87 +1605,87 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" s="11" t="b">
+      <c r="A41" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C42" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
+      <c r="B44" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C43" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C44" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="11" t="b">
-        <v>0</v>
+      <c r="B45" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="B46" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" s="25" t="b">
+      <c r="A46" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B47" s="2" t="s">
+      <c r="A47" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C47" s="11" t="b">
+      <c r="C47" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B48" s="1" t="s">
+      <c r="A48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="10" t="b">
@@ -1705,21 +1693,21 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B49" s="2" t="s">
+      <c r="A49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C49" s="11" t="b">
+      <c r="C49" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B50" s="1" t="s">
+      <c r="A50" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="10" t="b">
@@ -1727,21 +1715,21 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B51" s="2" t="s">
+      <c r="A51" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C51" s="11" t="b">
+      <c r="C51" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B52" s="1" t="s">
+      <c r="A52" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="10" t="b">
@@ -1749,21 +1737,21 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B53" s="2" t="s">
+      <c r="A53" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C53" s="11" t="b">
+      <c r="C53" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B54" s="1" t="s">
+      <c r="A54" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C54" s="10" t="b">
@@ -1771,21 +1759,21 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B55" s="2" t="s">
+      <c r="A55" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C55" s="11" t="b">
+      <c r="C55" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B56" s="1" t="s">
+      <c r="A56" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C56" s="10" t="b">
@@ -1794,232 +1782,232 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C57" s="11" t="b">
+        <v>68</v>
+      </c>
+      <c r="C57" s="10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C58" s="11" t="b">
+      <c r="C58" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>69</v>
+      <c r="B59" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C59" s="10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C60" s="11" t="b">
+      <c r="B60" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>69</v>
+      <c r="B61" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C61" s="10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C62" s="11" t="b">
+      <c r="B62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>69</v>
+      <c r="B63" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C63" s="10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64" s="11" t="b">
+      <c r="B64" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>69</v>
+      <c r="B65" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C65" s="10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C66" s="11" t="b">
+      <c r="B66" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C66" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>69</v>
+      <c r="A67" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C67" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C68" s="11" t="b">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C68" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C69" s="11" t="b">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="C69" s="10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C70" s="11" t="b">
-        <v>1</v>
+      <c r="A70" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C71" s="10" t="b">
-        <v>1</v>
+      <c r="A71" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" s="2" t="s">
+      <c r="A72" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C72" s="11" t="b">
-        <v>0</v>
+      <c r="C72" s="12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" s="10" t="b">
-        <v>0</v>
+      <c r="A73" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C74" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" s="13" t="b">
+      <c r="A75" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C75" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B76" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B76" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C76" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B77" s="4" t="s">
+      <c r="A77" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C77" s="13" t="b">
+      <c r="C77" s="11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2027,7 +2015,7 @@
       <c r="A78" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C78" s="12" t="b">
@@ -2035,82 +2023,50 @@
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="9" t="s">
+      <c r="A79" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C79" s="13" t="b">
+      <c r="C79" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="8" t="s">
-        <v>96</v>
+      <c r="A80" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C80" s="12" t="b">
-        <v>1</v>
+        <v>84</v>
+      </c>
+      <c r="C80" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C81" s="13" t="b">
-        <v>1</v>
+      <c r="A81" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B81" s="17"/>
+      <c r="C81" s="18" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C82" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C83" s="12" t="b">
-        <v>0</v>
-      </c>
+      <c r="A82" s="16"/>
+      <c r="B82" s="17"/>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B84" s="18"/>
-      <c r="C84" s="19" t="b">
-        <v>0</v>
+      <c r="C84">
+        <f>COUNTIF(Table1[Paid],TRUE)</f>
+        <v>57</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="17"/>
-      <c r="B85" s="18"/>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C87">
-        <f>COUNTIF(Table1[Paid],TRUE)</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C88">
-        <v>83</v>
+      <c r="C85">
+        <f>C84/83*100</f>
+        <v>68.674698795180717</v>
       </c>
     </row>
   </sheetData>

--- a/Payments.xlsx
+++ b/Payments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\USER-PC\Ravens\Senior Open 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E852B6-D62F-4248-85E8-BEBD3B75BFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175C553F-3316-4999-A626-852AF591A8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{20FD19A6-D5EB-470E-BA3E-64F28732135B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="98">
   <si>
     <t>Le Roux Strydom</t>
   </si>
@@ -71,9 +71,6 @@
     <t>Dirk Coetzee</t>
   </si>
   <si>
-    <t>Tayla Bailey</t>
-  </si>
-  <si>
     <t>Adam Domingo</t>
   </si>
   <si>
@@ -95,9 +92,6 @@
     <t>Tashreeq Samodien</t>
   </si>
   <si>
-    <t>Kirk Daries</t>
-  </si>
-  <si>
     <t>Sedick Abrahams</t>
   </si>
   <si>
@@ -336,6 +330,9 @@
   </si>
   <si>
     <t>Paid</t>
+  </si>
+  <si>
+    <t>Lindsay October</t>
   </si>
 </sst>
 </file>
@@ -662,6 +659,44 @@
           <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="medium">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color auto="1"/>
@@ -689,26 +724,6 @@
           <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color auto="1"/>
@@ -724,24 +739,6 @@
         </bottom>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="medium">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -825,15 +822,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C3AAE3A1-2292-44A8-9A60-4F25F509993E}" name="Table1" displayName="Table1" ref="A1:C82" totalsRowCount="1" headerRowBorderDxfId="6" tableBorderDxfId="5">
-  <autoFilter ref="A1:C81" xr:uid="{C3AAE3A1-2292-44A8-9A60-4F25F509993E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C81">
-    <sortCondition ref="B1:B81"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C3AAE3A1-2292-44A8-9A60-4F25F509993E}" name="Table1" displayName="Table1" ref="A1:C81" totalsRowCount="1" headerRowBorderDxfId="6" tableBorderDxfId="5">
+  <autoFilter ref="A1:C80" xr:uid="{C3AAE3A1-2292-44A8-9A60-4F25F509993E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C80">
+    <sortCondition ref="B1:B80"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{7626E09E-2B1B-418C-9849-29381AA54924}" name="Name" dataDxfId="4" totalsRowDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{16A0F98D-43CC-4CB8-8BA0-7D19F26407D7}" name="Club" dataDxfId="2" totalsRowDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{3EE74F1F-3239-48C8-9A34-81F7D990581E}" name="Paid" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{7626E09E-2B1B-418C-9849-29381AA54924}" name="Name" dataDxfId="4" totalsRowDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{16A0F98D-43CC-4CB8-8BA0-7D19F26407D7}" name="Club" dataDxfId="3" totalsRowDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{3EE74F1F-3239-48C8-9A34-81F7D990581E}" name="Paid" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1156,7 +1153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CA27C5-37ED-429D-8AC1-0ED926991F49}">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1166,21 +1163,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>96</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C2" s="23" t="b">
         <v>0</v>
@@ -1188,10 +1185,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C3" s="9" t="b">
         <v>1</v>
@@ -1199,10 +1196,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C4" s="10" t="b">
         <v>1</v>
@@ -1210,10 +1207,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C5" s="9" t="b">
         <v>0</v>
@@ -1221,10 +1218,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C6" s="10" t="b">
         <v>1</v>
@@ -1232,10 +1229,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C7" s="9" t="b">
         <v>0</v>
@@ -1243,10 +1240,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8" s="10" t="b">
         <v>0</v>
@@ -1254,10 +1251,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C9" s="9" t="b">
         <v>0</v>
@@ -1265,10 +1262,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C10" s="10" t="b">
         <v>0</v>
@@ -1276,10 +1273,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11" s="9" t="b">
         <v>0</v>
@@ -1287,10 +1284,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12" s="10" t="b">
         <v>1</v>
@@ -1298,10 +1295,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13" s="9" t="b">
         <v>1</v>
@@ -1309,10 +1306,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" s="10" t="b">
         <v>1</v>
@@ -1320,10 +1317,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C15" s="9" t="b">
         <v>0</v>
@@ -1331,10 +1328,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C16" s="10" t="b">
         <v>1</v>
@@ -1342,10 +1339,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17" s="9" t="b">
         <v>1</v>
@@ -1353,10 +1350,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C18" s="10" t="b">
         <v>1</v>
@@ -1364,10 +1361,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C19" s="9" t="b">
         <v>1</v>
@@ -1375,10 +1372,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20" s="10" t="b">
         <v>1</v>
@@ -1386,10 +1383,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="9" t="b">
         <v>1</v>
@@ -1451,622 +1448,611 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="10" t="b">
+      <c r="C27" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="9" t="b">
-        <v>0</v>
+      <c r="A28" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="B30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="B31" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+      <c r="B32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+      <c r="B33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="B34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="10" t="b">
+      <c r="B35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C36" s="9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C37" s="9" t="b">
-        <v>0</v>
+      <c r="A37" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="10" t="b">
+      <c r="A38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="9" t="b">
+      <c r="A39" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="10" t="b">
+      <c r="A40" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C41" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
+      <c r="B42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C42" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
+      <c r="B43" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C43" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C44" s="10" t="b">
+      <c r="B44" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="24" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="B45" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C45" s="24" t="b">
+      <c r="A45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+      <c r="B47" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
+      <c r="B48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C48" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
+      <c r="B49" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C49" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
+      <c r="B50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
+      <c r="B51" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C51" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
+      <c r="B52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C52" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C52" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+      <c r="B53" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C53" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
+      <c r="B54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C54" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C55" s="9" t="b">
+      <c r="B55" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" s="10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="C56" s="10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C57" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
+      <c r="B58" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C58" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C58" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
+      <c r="B59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C59" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
+      <c r="B60" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C60" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
+      <c r="B61" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C61" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C61" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
+      <c r="B62" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C62" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
+      <c r="B63" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C63" s="9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C63" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="s">
+      <c r="B64" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C64" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C64" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C65" s="10" t="b">
+      <c r="B65" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C65" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C66" s="9" t="b">
+      <c r="A66" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C66" s="10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C67" s="10" t="b">
+      <c r="A67" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C67" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C68" s="9" t="b">
-        <v>1</v>
+      <c r="A68" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" s="10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" s="10" t="b">
+      <c r="C69" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" s="9" t="b">
-        <v>0</v>
+      <c r="B70" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" s="11" t="b">
-        <v>0</v>
+      <c r="A71" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" s="12" t="b">
+      <c r="A72" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
+      <c r="A73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B73" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C73" s="11" t="b">
+      <c r="C73" s="12" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C74" s="12" t="b">
+      <c r="A74" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
+      <c r="A75" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C75" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="8" t="s">
+      <c r="B76" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="B76" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C76" s="12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
+      <c r="B77" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C77" s="11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C78" s="12" t="b">
-        <v>1</v>
+      <c r="B78" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" s="11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="C79" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C80" s="11" t="b">
+      <c r="A80" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B80" s="17"/>
+      <c r="C80" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="16" t="s">
-        <v>64</v>
-      </c>
+      <c r="A81" s="16"/>
       <c r="B81" s="17"/>
-      <c r="C81" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="16"/>
-      <c r="B82" s="17"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C83">
+        <f>COUNTIF(Table1[Paid],TRUE)</f>
+        <v>58</v>
+      </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C84">
-        <f>COUNTIF(Table1[Paid],TRUE)</f>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C85">
-        <f>C84/83*100</f>
-        <v>68.674698795180717</v>
+        <f>C83/83*100</f>
+        <v>69.879518072289159</v>
       </c>
     </row>
   </sheetData>

--- a/Payments.xlsx
+++ b/Payments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\USER-PC\Ravens\Senior Open 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175C553F-3316-4999-A626-852AF591A8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0616EC-561B-4758-B160-7AE330D13D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{20FD19A6-D5EB-470E-BA3E-64F28732135B}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{20FD19A6-D5EB-470E-BA3E-64F28732135B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="100">
   <si>
     <t>Le Roux Strydom</t>
   </si>
@@ -333,13 +333,19 @@
   </si>
   <si>
     <t>Lindsay October</t>
+  </si>
+  <si>
+    <t>Kamiel Ebrahim</t>
+  </si>
+  <si>
+    <t>Mother City</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -349,6 +355,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -573,7 +586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -641,6 +654,34 @@
       </extLst>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
@@ -822,10 +863,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C3AAE3A1-2292-44A8-9A60-4F25F509993E}" name="Table1" displayName="Table1" ref="A1:C81" totalsRowCount="1" headerRowBorderDxfId="6" tableBorderDxfId="5">
-  <autoFilter ref="A1:C80" xr:uid="{C3AAE3A1-2292-44A8-9A60-4F25F509993E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C80">
-    <sortCondition ref="B1:B80"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C3AAE3A1-2292-44A8-9A60-4F25F509993E}" name="Table1" displayName="Table1" ref="A1:C82" totalsRowCount="1" headerRowBorderDxfId="6" tableBorderDxfId="5">
+  <autoFilter ref="A1:C81" xr:uid="{C3AAE3A1-2292-44A8-9A60-4F25F509993E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C81">
+    <sortCondition ref="B1:B81"/>
   </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{7626E09E-2B1B-418C-9849-29381AA54924}" name="Name" dataDxfId="4" totalsRowDxfId="1"/>
@@ -1153,15 +1194,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CA27C5-37ED-429D-8AC1-0ED926991F49}">
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>94</v>
       </c>
@@ -1172,7 +1214,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>63</v>
       </c>
@@ -1180,10 +1222,10 @@
         <v>64</v>
       </c>
       <c r="C2" s="23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>76</v>
       </c>
@@ -1194,7 +1236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>59</v>
       </c>
@@ -1205,7 +1247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>78</v>
       </c>
@@ -1213,10 +1255,10 @@
         <v>58</v>
       </c>
       <c r="C5" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>56</v>
       </c>
@@ -1226,8 +1268,14 @@
       <c r="C6" s="10" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>30</v>
       </c>
@@ -1237,8 +1285,14 @@
       <c r="C7" s="9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>32</v>
       </c>
@@ -1248,8 +1302,14 @@
       <c r="C8" s="10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>33</v>
       </c>
@@ -1259,8 +1319,14 @@
       <c r="C9" s="9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>34</v>
       </c>
@@ -1270,8 +1336,14 @@
       <c r="C10" s="10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>35</v>
       </c>
@@ -1281,8 +1353,14 @@
       <c r="C11" s="9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>36</v>
       </c>
@@ -1292,8 +1370,14 @@
       <c r="C12" s="10" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
@@ -1303,8 +1387,14 @@
       <c r="C13" s="9" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>38</v>
       </c>
@@ -1314,8 +1404,14 @@
       <c r="C14" s="10" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
@@ -1325,140 +1421,152 @@
       <c r="C15" s="9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="G15" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="C16" s="31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="C17" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="C18" s="31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="C19" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="C20" s="31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="C21" s="27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="C22" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" s="28"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="C23" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" s="28"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="C24" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="D24" s="28"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="C25" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="28"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="C26" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" s="28"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C27" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" s="28"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>40</v>
       </c>
@@ -1469,7 +1577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>42</v>
       </c>
@@ -1480,7 +1588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>43</v>
       </c>
@@ -1491,7 +1599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>44</v>
       </c>
@@ -1502,7 +1610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>45</v>
       </c>
@@ -1554,7 +1662,7 @@
         <v>61</v>
       </c>
       <c r="C36" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1976,14 +2084,14 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C75" s="12" t="b">
-        <v>0</v>
+      <c r="C75" s="34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -2016,7 +2124,7 @@
         <v>12</v>
       </c>
       <c r="C78" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -2032,27 +2140,38 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B80" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C80" s="18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B80" s="17"/>
-      <c r="C80" s="18" t="b">
+      <c r="B81" s="17"/>
+      <c r="C81" s="18" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="16"/>
-      <c r="B81" s="17"/>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C83">
-        <f>COUNTIF(Table1[Paid],TRUE)</f>
-        <v>58</v>
-      </c>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="16"/>
+      <c r="B82" s="17"/>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C84">
-        <f>C83/83*100</f>
-        <v>69.879518072289159</v>
+        <f>COUNTIF(Table1[Paid],TRUE)</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C85">
+        <f>C84/79*100</f>
+        <v>88.60759493670885</v>
       </c>
     </row>
   </sheetData>
